--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0190.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0190.xlsx
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Cảm ơn, {PlayerName}! Cậu đã giúp bọn tôi rất nhiều!</t>
+          <t>Cảm ơn, {PlayerName}! bạn đã giúp bọn tôi rất nhiều!</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Ta nhớ ngươi.</t>
+          <t>Tao nhớ mày.</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Bạn là...?</t>
+          <t>Cậu là... ai?</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Ta nhớ ngươi.</t>
+          <t>Tao nhớ mày.</t>
         </is>
       </c>
     </row>
